--- a/audit_report_ALL_TEAM_03_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_03_Oct_2026.xlsx
@@ -483,13 +483,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW2"/>
+  <dimension ref="A1:AW3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -851,10 +851,8 @@
           <t>Roshan Shrestha</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9700971170</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9700971170</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -944,50 +942,149 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>1,15</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.33794</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.33794</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS2" s="3" t="inlineStr">
+        <is>
+          <t>2d 11h 39m</t>
+        </is>
+      </c>
+      <c r="AT2" s="3" t="inlineStr">
+        <is>
+          <t>4d 13h 52m</t>
+        </is>
+      </c>
+      <c r="AU2" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV2" s="3" t="inlineStr">
+        <is>
           <t>Case : worst internet service   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS2" s="3" t="inlineStr">
-        <is>
-          <t>2d 11h 39m</t>
-        </is>
-      </c>
-      <c r="AT2" s="3" t="inlineStr">
-        <is>
-          <t>4d 13h 52m</t>
-        </is>
-      </c>
-      <c r="AU2" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV2" s="3" t="inlineStr">
-        <is>
-          <t>Case : worst internet service   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW2" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 9:50 AM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="inlineStr"/>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr"/>
+      <c r="V3" s="3" t="inlineStr"/>
+      <c r="W3" s="3" t="inlineStr"/>
+      <c r="X3" s="3" t="inlineStr"/>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr"/>
+      <c r="AA3" s="3" t="inlineStr"/>
+      <c r="AB3" s="3" t="inlineStr"/>
+      <c r="AC3" s="3" t="inlineStr"/>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr"/>
+      <c r="AF3" s="3" t="inlineStr"/>
+      <c r="AG3" s="3" t="inlineStr"/>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr"/>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr"/>
+      <c r="AM3" s="3" t="inlineStr"/>
+      <c r="AN3" s="3" t="inlineStr"/>
+      <c r="AO3" s="3" t="inlineStr"/>
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1099,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1039,7 +1136,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1136,134 +1233,163 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr"/>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Slow Internet Connection</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Video content is Buffering</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C15" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="3" t="inlineStr"/>
+      <c r="B16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
         </is>

--- a/audit_report_ALL_TEAM_03_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_03_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW3"/>
+  <dimension ref="A1:AW4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -496,17 +496,17 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="27" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
@@ -517,19 +517,19 @@
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="22" customWidth="1" min="32" max="32"/>
+    <col width="23" customWidth="1" min="32" max="32"/>
     <col width="29" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
-    <col width="10" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="13" customWidth="1" min="38" max="38"/>
+    <col width="14" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1088,6 +1088,209 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 9:56 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355412</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Mukunda  Prasad Khatiwada</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Mukunda  Prasad Khatiwada</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9841928735</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 09:56:56 AM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>CHB9841928735</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:26:17 PM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 09:56:56 AM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Shramsheel Vidyapith Nepal ??????? ????????? ????? School - School P95J+MQW Kageshwori Manohara 4460</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>9841928735@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>05:34 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>L25-6</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>19h 30m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1099,7 +1302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1107,12 +1310,12 @@
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="27" customWidth="1" min="11" max="11"/>
     <col width="35" customWidth="1" min="12" max="12"/>
     <col width="34" customWidth="1" min="13" max="13"/>
   </cols>
@@ -1136,7 +1339,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -1146,7 +1349,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -1157,7 +1360,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1372,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>0m</t>
         </is>
       </c>
     </row>
@@ -1181,7 +1384,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>19h 30m</t>
         </is>
       </c>
     </row>
@@ -1218,180 +1421,288 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr"/>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
       <c r="B11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr"/>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Slow Internet Connection</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Video content is Buffering</t>
         </is>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C17" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D17" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr"/>
-      <c r="B16" s="3" t="inlineStr"/>
-      <c r="C16" s="3" t="n">
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr"/>
+      <c r="B18" s="3" t="inlineStr"/>
+      <c r="C18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355412</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Mukunda  Prasad Khatiwada</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 09:56:56 AM</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:26:17 PM</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 09:56:56 AM</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>19h 30m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_03_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_03_Oct_2026.xlsx
@@ -483,11 +483,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW4"/>
+  <dimension ref="A1:AW7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -512,19 +512,19 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="27" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="23" customWidth="1" min="32" max="32"/>
+    <col width="31" customWidth="1" min="32" max="32"/>
     <col width="29" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="14" customWidth="1" min="38" max="38"/>
-    <col width="20" customWidth="1" min="39" max="39"/>
+    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
@@ -1155,10 +1155,8 @@
           <t>Mukunda  Prasad Khatiwada</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9841928735</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9841928735</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1248,10 +1246,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
@@ -1262,32 +1258,657 @@
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>19h 30m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS4" s="3" t="inlineStr">
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 10:20 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355678</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>sabita karki</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>sabita karki</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9860879402</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 10:20:27 AM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9745663222</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 05:14:25 PM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 10:20:27 AM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>27.67412</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>Bhat-Bhateni Koteshwor M8FV+WR3, ???????? ?????, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>prativayadav36@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>03:06 hour</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>CDB432</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>85.3462</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT4" s="3" t="inlineStr">
-        <is>
-          <t>19h 30m</t>
-        </is>
-      </c>
-      <c r="AU4" s="3" t="inlineStr">
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>17h 6m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV4" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW4" s="3" t="inlineStr">
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 10:30 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355036</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Nirjala Lekhak</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Nirjala Lekhak</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9851132775</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 11:45:08 AM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9867134084</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 11:45:08 AM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 10:30:08 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>27.691249</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>waiting dhungaadda dhungeadda, chandragiri 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>lekhaknirjala@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr"/>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>CDB527</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>85.267541</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>22h 45m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>22h 45m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 10:30 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355553</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Santosh Khatiwada</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Santosh Khatiwada</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9849058014</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 10:30:57 AM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9849058014</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 03:55:48 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 10:30:57 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Near Kathmandu Institute of Technology (KIT College), Milan Tole, Tokha Road, Kathmandu GPO Box No.</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>khatiwadasantosh82@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>04:35 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>L15-4</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr"/>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>18h 35m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1339,7 +1960,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -1349,7 +1970,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1360,7 +1981,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1384,7 +2005,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>19h 30m</t>
+          <t>18h 23m</t>
         </is>
       </c>
     </row>
@@ -1425,14 +2046,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -1515,14 +2136,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -1672,14 +2293,14 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
           <t>03 Oct 2026 09:56:56 AM</t>
@@ -1703,6 +2324,140 @@
       <c r="M22" s="3" t="inlineStr">
         <is>
           <t>19h 30m</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>TKT1355678</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>sabita karki</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 10:20:27 AM</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 05:14:25 PM</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 10:20:27 AM</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>17h 6m</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355553</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Santosh Khatiwada</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 10:30:57 AM</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 03:55:48 PM</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 10:30:57 AM</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>18h 35m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_03_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_03_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW7"/>
+  <dimension ref="A1:AW8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1354,10 +1354,8 @@
           <t>sabita karki</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9860879402</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9860879402</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1451,25 +1449,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>CDB432</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.3462</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.3462</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
@@ -1565,10 +1559,8 @@
           <t>Nirjala Lekhak</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9851132775</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9851132775</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -1658,25 +1650,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>CDB527</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>85.267541</t>
-        </is>
+      <c r="AP6" s="3" t="n">
+        <v>85.26754099999999</v>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
@@ -1772,10 +1760,8 @@
           <t>Santosh Khatiwada</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9849058014</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9849058014</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -1847,10 +1833,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH7" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH7" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI7" s="3" t="inlineStr">
         <is>
@@ -1869,10 +1853,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
@@ -1883,30 +1865,241 @@
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>18h 35m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS7" s="3" t="inlineStr">
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 10:37 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355571</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Puran  Kumar shrestha</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Puran  Kumar shrestha</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9803427273</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 10:37:39 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9803427273</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 04:05:32 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 10:37:39 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.752476</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Tokha Rd, Kathmandu 44600 Near by Hamro Dental Clinic, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>puran.shrestha50@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>04:32 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>L16-3</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.326974</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT7" s="3" t="inlineStr">
-        <is>
-          <t>18h 35m</t>
-        </is>
-      </c>
-      <c r="AU7" s="3" t="inlineStr">
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>18h 32m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV7" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW7" s="3" t="inlineStr">
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -1923,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1960,7 +2153,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -1970,7 +2163,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1981,7 +2174,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2198,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>18h 23m</t>
+          <t>18h 25m</t>
         </is>
       </c>
     </row>
@@ -2046,14 +2239,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -2136,14 +2329,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D16" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2553,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
@@ -2427,14 +2620,14 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
           <t>03 Oct 2026 10:30:57 AM</t>
@@ -2458,6 +2651,73 @@
       <c r="M24" s="3" t="inlineStr">
         <is>
           <t>18h 35m</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>TKT1355571</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Puran  Kumar shrestha</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 10:37:39 AM</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 04:05:32 PM</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 10:37:39 AM</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>18h 32m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_03_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_03_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW8"/>
+  <dimension ref="A1:AW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -1961,10 +1961,8 @@
           <t>Puran  Kumar shrestha</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9803427273</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9803427273</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2058,48 +2056,466 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>L16-3</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.326974</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.32697400000001</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>18h 32m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS8" s="3" t="inlineStr">
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:02 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1354592</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Santosh Shrestha</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Santosh Shrestha</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9860119260</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:02:13 AM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9841748714</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:02:11 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:02:13 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>27.69329</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>27.709118048408175, 85.40087268146168, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>santoshshresthag@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>11:02 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>L46-3</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>85.31063</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT8" s="3" t="inlineStr">
-        <is>
-          <t>18h 32m</t>
-        </is>
-      </c>
-      <c r="AU8" s="3" t="inlineStr">
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>1d 14h</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV8" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW8" s="3" t="inlineStr">
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 10:53 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355782</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>subesh puri</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>subesh puri</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9861059460</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 10:53:31 AM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9861059460</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 06:14:50 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 10:53:31 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu - Santinagar / New Baneshwor near Ananda Evenet -, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>purisubesh9@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>02:39 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>L23-5</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>16h 38m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -2116,7 +2532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2153,7 +2569,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -2163,7 +2579,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -2174,7 +2590,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2614,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>18h 25m</t>
+          <t>21h 23m</t>
         </is>
       </c>
     </row>
@@ -2239,14 +2655,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -2329,14 +2745,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -2687,14 +3103,14 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
           <t>03 Oct 2026 10:37:39 AM</t>
@@ -2718,6 +3134,140 @@
       <c r="M25" s="5" t="inlineStr">
         <is>
           <t>18h 32m</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1354592</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Santosh Shrestha</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:02:13 AM</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 09:02:11 PM</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:02:13 AM</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>1d 14h</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>TKT1355782</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>subesh puri</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 10:53:31 AM</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 06:14:50 PM</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 10:53:31 AM</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>16h 38m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_03_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_03_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW10"/>
+  <dimension ref="A1:AW13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2166,10 +2166,8 @@
           <t>Santosh Shrestha</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9860119260</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9860119260</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2263,25 +2261,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>L46-3</t>
         </is>
       </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>85.31063</t>
-        </is>
+      <c r="AP9" s="3" t="n">
+        <v>85.31063</v>
       </c>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
@@ -2377,10 +2371,8 @@
           <t>subesh puri</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9861059460</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9861059460</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2474,48 +2466,461 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>L23-5</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>16h 38m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
           <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS10" s="3" t="inlineStr">
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:04 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr"/>
+      <c r="V11" s="3" t="inlineStr"/>
+      <c r="W11" s="3" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr"/>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr"/>
+      <c r="AA11" s="3" t="inlineStr"/>
+      <c r="AB11" s="3" t="inlineStr"/>
+      <c r="AC11" s="3" t="inlineStr"/>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr"/>
+      <c r="AF11" s="3" t="inlineStr"/>
+      <c r="AG11" s="3" t="inlineStr"/>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr"/>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr"/>
+      <c r="AM11" s="3" t="inlineStr"/>
+      <c r="AN11" s="3" t="inlineStr"/>
+      <c r="AO11" s="3" t="inlineStr"/>
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:14 AM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr"/>
+      <c r="K12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr"/>
+      <c r="M12" s="3" t="inlineStr"/>
+      <c r="N12" s="3" t="inlineStr"/>
+      <c r="O12" s="3" t="inlineStr"/>
+      <c r="P12" s="3" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr"/>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr"/>
+      <c r="V12" s="3" t="inlineStr"/>
+      <c r="W12" s="3" t="inlineStr"/>
+      <c r="X12" s="3" t="inlineStr"/>
+      <c r="Y12" s="3" t="inlineStr"/>
+      <c r="Z12" s="3" t="inlineStr"/>
+      <c r="AA12" s="3" t="inlineStr"/>
+      <c r="AB12" s="3" t="inlineStr"/>
+      <c r="AC12" s="3" t="inlineStr"/>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr"/>
+      <c r="AF12" s="3" t="inlineStr"/>
+      <c r="AG12" s="3" t="inlineStr"/>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr"/>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr"/>
+      <c r="AM12" s="3" t="inlineStr"/>
+      <c r="AN12" s="3" t="inlineStr"/>
+      <c r="AO12" s="3" t="inlineStr"/>
+      <c r="AP12" s="3" t="inlineStr"/>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:13 AM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1354797</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Shreyak Timsina</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Shreyak Timsina</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9863626262</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:13:21 AM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9863626262</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 09:20:39 AM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:13:21 AM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>27.691212</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>M8RF+FCM, Radha Krishna Marg, Kathmandu 44600,Department of Commerce, Supplies and Consumer Protecti</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>shreyaktimsina29@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>11:13 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>L63-4</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>85.323547</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT10" s="3" t="inlineStr">
-        <is>
-          <t>16h 38m</t>
-        </is>
-      </c>
-      <c r="AU10" s="3" t="inlineStr">
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 52m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV10" s="3" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW10" s="3" t="inlineStr">
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -2532,7 +2937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2569,7 +2974,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -2579,7 +2984,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -2590,7 +2995,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -2614,7 +3019,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>21h 23m</t>
+          <t>22h 2m</t>
         </is>
       </c>
     </row>
@@ -2655,14 +3060,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>6</v>
-      </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -2745,14 +3150,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D16" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="D16" s="3" t="n">
-        <v>6</v>
-      </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>87.5%</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3575,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
@@ -3237,14 +3642,14 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
           <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
           <t>03 Oct 2026 10:53:31 AM</t>
@@ -3268,6 +3673,73 @@
       <c r="M27" s="5" t="inlineStr">
         <is>
           <t>16h 38m</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1354797</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Shreyak Timsina</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:13:21 AM</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 09:20:39 AM</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:13:21 AM</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 52m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_03_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_03_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW13"/>
+  <dimension ref="A1:AW15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2782,10 +2782,8 @@
           <t>Shreyak Timsina</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9863626262</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9863626262</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -2879,48 +2877,450 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>L63-4</t>
         </is>
       </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>85.323547</t>
-        </is>
+      <c r="AP13" s="3" t="n">
+        <v>85.323547</v>
       </c>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 52m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS13" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT13" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 52m</t>
-        </is>
-      </c>
-      <c r="AU13" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV13" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:27 AM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355395</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Susma Rai</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Susma Rai</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9803098080</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:17:58 AM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9803098080</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:18:02 PM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:27:03 AM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>27.75998</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Q843+M82, Tarakeshwar 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr"/>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr"/>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>L14-2</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>85.3051</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>9m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>21h 9m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:17 AM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355395</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Susma Rai</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Susma Rai</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9803098080</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:17:58 AM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>9803098080</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:18:02 PM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:27:03 AM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>27.75998</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>Q843+M82, Tarakeshwar 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr"/>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr"/>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>L14-2</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>85.3051</t>
+        </is>
+      </c>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>9m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>21h 9m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -2946,7 +3346,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2974,7 +3374,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -2995,7 +3395,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3060,14 +3460,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>7</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -3150,14 +3550,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>7</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>70.0%</t>
         </is>
       </c>
     </row>
@@ -3709,7 +4109,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_03_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_03_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW15"/>
+  <dimension ref="A1:AW17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2987,10 +2987,8 @@
           <t>Susma Rai</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9803098080</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9803098080</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3076,25 +3074,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>L14-2</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>85.3051</t>
-        </is>
+      <c r="AP14" s="3" t="n">
+        <v>85.3051</v>
       </c>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
@@ -3190,10 +3184,8 @@
           <t>Susma Rai</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9803098080</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9803098080</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -3279,48 +3271,454 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
           <t>L14-2</t>
         </is>
       </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>85.3051</t>
-        </is>
+      <c r="AP15" s="3" t="n">
+        <v>85.3051</v>
       </c>
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>9m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>21h 9m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS15" s="3" t="inlineStr">
-        <is>
-          <t>9m</t>
-        </is>
-      </c>
-      <c r="AT15" s="3" t="inlineStr">
-        <is>
-          <t>21h 9m</t>
-        </is>
-      </c>
-      <c r="AU15" s="3" t="inlineStr">
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:37 AM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1356143</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Pemchheku Sherpa</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Pemchheku Sherpa</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9860643065</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:37:04 AM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>9860643065</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 08:10:26 AM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:37:04 AM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>27.744118</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>tokha ward5 namuna tole, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr"/>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>01:37 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>L3-2</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>85.33054</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>3h 26m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:33 AM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355038</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Chandra Magar</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Chandra Magar</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9843092541</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:33:33 AM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>9843092541</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 11:46:50 AM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:33:33 AM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr"/>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>near by Sunflower Academy (English Medium SS) - School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>mgrchandra9899@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI17" s="3" t="inlineStr"/>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>2,8</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr"/>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>23h 46m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
         <is>
           <t>Other / In Progress (On Hold)</t>
         </is>
       </c>
-      <c r="AV15" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW15" s="3" t="inlineStr">
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -3337,7 +3735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3346,7 +3744,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3374,7 +3772,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -3384,7 +3782,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -3419,7 +3817,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>22h 2m</t>
+          <t>19h 42m</t>
         </is>
       </c>
     </row>
@@ -3460,14 +3858,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -3550,14 +3948,14 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -4143,6 +4541,73 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>TKT1356143</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Pemchheku Sherpa</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:37:04 AM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 08:10:26 AM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:37:04 AM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>3h 26m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_03_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_03_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW17"/>
+  <dimension ref="A1:AW19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="25" customWidth="1" min="9" max="9"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="28" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -518,7 +518,7 @@
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="31" customWidth="1" min="32" max="32"/>
-    <col width="29" customWidth="1" min="33" max="33"/>
+    <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -3381,10 +3381,8 @@
           <t>Pemchheku Sherpa</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9860643065</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9860643065</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -3474,25 +3472,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>L3-2</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>85.33054</t>
-        </is>
+      <c r="AP16" s="3" t="n">
+        <v>85.33054</v>
       </c>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
@@ -3588,10 +3582,8 @@
           <t>Chandra Magar</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9843092541</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9843092541</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -3663,10 +3655,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH17" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH17" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI17" s="3" t="inlineStr"/>
       <c r="AJ17" s="3" t="inlineStr"/>
@@ -3681,10 +3671,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
@@ -3695,32 +3683,338 @@
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>23h 46m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS17" s="3" t="inlineStr">
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:50 AM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr"/>
+      <c r="K18" s="3" t="inlineStr"/>
+      <c r="L18" s="3" t="inlineStr"/>
+      <c r="M18" s="3" t="inlineStr"/>
+      <c r="N18" s="3" t="inlineStr"/>
+      <c r="O18" s="3" t="inlineStr"/>
+      <c r="P18" s="3" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr"/>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr"/>
+      <c r="V18" s="3" t="inlineStr"/>
+      <c r="W18" s="3" t="inlineStr"/>
+      <c r="X18" s="3" t="inlineStr"/>
+      <c r="Y18" s="3" t="inlineStr"/>
+      <c r="Z18" s="3" t="inlineStr"/>
+      <c r="AA18" s="3" t="inlineStr"/>
+      <c r="AB18" s="3" t="inlineStr"/>
+      <c r="AC18" s="3" t="inlineStr"/>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr"/>
+      <c r="AF18" s="3" t="inlineStr"/>
+      <c r="AG18" s="3" t="inlineStr"/>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr"/>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr"/>
+      <c r="AM18" s="3" t="inlineStr"/>
+      <c r="AN18" s="3" t="inlineStr"/>
+      <c r="AO18" s="3" t="inlineStr"/>
+      <c r="AP18" s="3" t="inlineStr"/>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:49 AM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : secondary router connection  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>secondary router connection</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355761</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Kabiraj Limbu</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Kabiraj Limbu</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9825986033</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:49:29 AM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>BKT9825986033</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 05:58:41 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:49:29 AM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr"/>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>Kageshwori Manohara Municipality Ward No.7 office - Local government office P92M+XX3 Kageshwori Mano</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>test@test.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Query For Secondary Router /Repeater</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>03:51 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Bhumika Saud</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>L37-1</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr"/>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : secondary router connection  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT17" s="3" t="inlineStr">
-        <is>
-          <t>23h 46m</t>
-        </is>
-      </c>
-      <c r="AU17" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV17" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW17" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>17h 50m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : secondary router connection  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -3735,13 +4029,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
@@ -3772,7 +4066,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -3782,7 +4076,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -3817,7 +4111,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>19h 42m</t>
+          <t>19h 30m</t>
         </is>
       </c>
     </row>
@@ -3858,14 +4152,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -3944,210 +4238,166 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Query For Secondary Router /Repeater</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr"/>
-      <c r="B18" s="3" t="inlineStr"/>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
       <c r="C18" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr"/>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+    <row r="20"/>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H21" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I21" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K21" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M21" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>TKT1355412</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Mukunda  Prasad Khatiwada</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>03 Oct 2026 09:56:56 AM</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>02 Oct 2026 02:26:17 PM</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>03 Oct 2026 09:56:56 AM</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>19h 30m</t>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>TKT1355678</t>
+          <t>TKT1355412</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>sabita karki</t>
+          <t>Mukunda  Prasad Khatiwada</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -4177,22 +4427,22 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 10:20:27 AM</t>
+          <t>03 Oct 2026 09:56:56 AM</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>02 Oct 2026 05:14:25 PM</t>
+          <t>02 Oct 2026 02:26:17 PM</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 10:20:27 AM</t>
+          <t>03 Oct 2026 09:56:56 AM</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
@@ -4202,19 +4452,19 @@
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>17h 6m</t>
+          <t>19h 30m</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>TKT1355553</t>
+          <t>TKT1355678</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Santosh Khatiwada</t>
+          <t>sabita karki</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -4244,22 +4494,22 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 10:30:57 AM</t>
+          <t>03 Oct 2026 10:20:27 AM</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>02 Oct 2026 03:55:48 PM</t>
+          <t>02 Oct 2026 05:14:25 PM</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 10:30:57 AM</t>
+          <t>03 Oct 2026 10:20:27 AM</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -4269,19 +4519,19 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>18h 35m</t>
+          <t>17h 6m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TKT1355571</t>
+          <t>TKT1355553</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Puran  Kumar shrestha</t>
+          <t>Santosh Khatiwada</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -4311,22 +4561,22 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 10:37:39 AM</t>
+          <t>03 Oct 2026 10:30:57 AM</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>02 Oct 2026 04:05:32 PM</t>
+          <t>02 Oct 2026 03:55:48 PM</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 10:37:39 AM</t>
+          <t>03 Oct 2026 10:30:57 AM</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
@@ -4336,19 +4586,19 @@
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>18h 32m</t>
+          <t>18h 35m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1354592</t>
+          <t>TKT1355571</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Santosh Shrestha</t>
+          <t>Puran  Kumar shrestha</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -4378,22 +4628,22 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 11:02:13 AM</t>
+          <t>03 Oct 2026 10:37:39 AM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 09:02:11 PM</t>
+          <t>02 Oct 2026 04:05:32 PM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 11:02:13 AM</t>
+          <t>03 Oct 2026 10:37:39 AM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -4403,19 +4653,19 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>1d 14h</t>
+          <t>18h 32m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1355782</t>
+          <t>TKT1354592</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>subesh puri</t>
+          <t>Santosh Shrestha</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -4445,22 +4695,22 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 10:53:31 AM</t>
+          <t>03 Oct 2026 11:02:13 AM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>02 Oct 2026 06:14:50 PM</t>
+          <t>01 Oct 2026 09:02:11 PM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 10:53:31 AM</t>
+          <t>03 Oct 2026 11:02:13 AM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -4470,19 +4720,19 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>16h 38m</t>
+          <t>1d 14h</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1354797</t>
+          <t>TKT1355782</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Shreyak Timsina</t>
+          <t>subesh puri</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -4512,22 +4762,22 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 11:13:21 AM</t>
+          <t>03 Oct 2026 10:53:31 AM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>02 Oct 2026 09:20:39 AM</t>
+          <t>02 Oct 2026 06:14:50 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 11:13:21 AM</t>
+          <t>03 Oct 2026 10:53:31 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -4537,74 +4787,208 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 52m</t>
+          <t>16h 38m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>TKT1354797</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Shreyak Timsina</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:13:21 AM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 09:20:39 AM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:13:21 AM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>1d 1h 52m</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
           <t>TKT1356143</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Pemchheku Sherpa</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D30" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F30" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
         <is>
           <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I30" s="3" t="inlineStr">
         <is>
           <t>03 Oct 2026 11:37:04 AM</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="J30" s="3" t="inlineStr">
         <is>
           <t>03 Oct 2026 08:10:26 AM</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="K30" s="3" t="inlineStr">
         <is>
           <t>03 Oct 2026 11:37:04 AM</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr">
+      <c r="L30" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M29" s="5" t="inlineStr">
+      <c r="M30" s="3" t="inlineStr">
         <is>
           <t>3h 26m</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>TKT1355761</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Kabiraj Limbu</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Query For Secondary Router /Repeater</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Case : secondary router connection  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Case : secondary router connection  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:49:29 AM</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 05:58:41 PM</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:49:29 AM</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>17h 50m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_03_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_03_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW19"/>
+  <dimension ref="A1:AW23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -497,7 +497,7 @@
     <col width="30" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="28" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
@@ -512,12 +512,12 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="27" customWidth="1" min="26" max="26"/>
-    <col width="19" customWidth="1" min="27" max="27"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
-    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
-    <col width="31" customWidth="1" min="32" max="32"/>
+    <col width="34" customWidth="1" min="32" max="32"/>
     <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -532,7 +532,7 @@
     <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="32" customWidth="1" min="47" max="47"/>
+    <col width="36" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
@@ -3882,10 +3882,8 @@
           <t>Kabiraj Limbu</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9825986033</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9825986033</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -3975,10 +3973,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
@@ -3989,32 +3985,864 @@
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>17h 50m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
           <t>Case : secondary router connection  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS19" s="3" t="inlineStr">
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:09 PM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355352</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Parkas Nepal</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Parkas Nepal</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9849025416</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:09:34 PM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>9849025416</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:03:59 PM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:09:34 PM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr">
+        <is>
+          <t>27.75259</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>Nepal Yoga Home Tarkeshwor-5, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr">
+        <is>
+          <t>parkasnepal423@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr"/>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>L62-4</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr">
+        <is>
+          <t>85.2867</t>
+        </is>
+      </c>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT19" s="3" t="inlineStr">
-        <is>
-          <t>17h 50m</t>
-        </is>
-      </c>
-      <c r="AU19" s="3" t="inlineStr">
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>22h 5m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:16 PM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>no internet</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1354384</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Saugat Kamal Upradi</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Saugat Kamal Upradi</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9808035363</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 07:50:52 PM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>KLK9808035363</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>01 Oct 2026 06:06:50 PM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:16:48 PM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>Core Team</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>27.693722365366416, 85.2815403618628 GPS Coordinates Nearest: KAT004-01-3/7-ADB031 (114m Road) Map:</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr">
+        <is>
+          <t>9808035363@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr"/>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Rita Singh</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>1,3</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>1d 16h 25m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>1d 18h 9m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : no internet  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:13 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355534</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Netra bahadur basnet</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Netra bahadur basnet</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9849751248</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:13:15 PM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>9849751248</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 03:42:55 PM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:13:15 PM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr"/>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>Sun City Apartments - Apartment building Kageshwori Manohara 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr">
+        <is>
+          <t>netrabahadurbasnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>06:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>L16-7</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr"/>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>20h 30m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV19" s="3" t="inlineStr">
-        <is>
-          <t>Case : secondary router connection  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW19" s="3" t="inlineStr">
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:05 PM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 router</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1354926</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Shreejan Shrestha</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Shreejan Shrestha</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9863229300</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:05:03 PM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>9863229300</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 10:25:56 AM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:05:03 PM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr">
+        <is>
+          <t>27.70256</t>
+        </is>
+      </c>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-customer care</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>Opposite of Chicken Station, Jhochhen, Nhoosa Marg, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>shreejan.shrestha2003@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr">
+        <is>
+          <t>11:40 hour</t>
+        </is>
+      </c>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr"/>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>2,1</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr">
+        <is>
+          <t>85.307746</t>
+        </is>
+      </c>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 39m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -4066,7 +4894,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -4076,7 +4904,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -4111,7 +4939,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>19h 30m</t>
+          <t>20h 9m</t>
         </is>
       </c>
     </row>
@@ -4152,14 +4980,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>69.2%</t>
+          <t>68.8%</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4998,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>0</v>
@@ -4265,10 +5093,10 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -4284,7 +5112,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Specific Website/App is slow</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -4300,171 +5128,127 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr"/>
-      <c r="B19" s="5" t="inlineStr"/>
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
       <c r="C19" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr"/>
+      <c r="B20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="20"/>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H22" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I22" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K22" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M22" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>TKT1355412</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Mukunda  Prasad Khatiwada</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>03 Oct 2026 09:56:56 AM</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>02 Oct 2026 02:26:17 PM</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>03 Oct 2026 09:56:56 AM</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>19h 30m</t>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>TKT1355678</t>
+          <t>TKT1355412</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>sabita karki</t>
+          <t>Mukunda  Prasad Khatiwada</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -4494,22 +5278,22 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 10:20:27 AM</t>
+          <t>03 Oct 2026 09:56:56 AM</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>02 Oct 2026 05:14:25 PM</t>
+          <t>02 Oct 2026 02:26:17 PM</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 10:20:27 AM</t>
+          <t>03 Oct 2026 09:56:56 AM</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -4519,19 +5303,19 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>17h 6m</t>
+          <t>19h 30m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TKT1355553</t>
+          <t>TKT1355678</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Santosh Khatiwada</t>
+          <t>sabita karki</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -4561,22 +5345,22 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 10:30:57 AM</t>
+          <t>03 Oct 2026 10:20:27 AM</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>02 Oct 2026 03:55:48 PM</t>
+          <t>02 Oct 2026 05:14:25 PM</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 10:30:57 AM</t>
+          <t>03 Oct 2026 10:20:27 AM</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
@@ -4586,19 +5370,19 @@
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>18h 35m</t>
+          <t>17h 6m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1355571</t>
+          <t>TKT1355553</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Puran  Kumar shrestha</t>
+          <t>Santosh Khatiwada</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -4628,22 +5412,22 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 10:37:39 AM</t>
+          <t>03 Oct 2026 10:30:57 AM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>02 Oct 2026 04:05:32 PM</t>
+          <t>02 Oct 2026 03:55:48 PM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 10:37:39 AM</t>
+          <t>03 Oct 2026 10:30:57 AM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -4653,19 +5437,19 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>18h 32m</t>
+          <t>18h 35m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1354592</t>
+          <t>TKT1355571</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Santosh Shrestha</t>
+          <t>Puran  Kumar shrestha</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -4695,22 +5479,22 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 11:02:13 AM</t>
+          <t>03 Oct 2026 10:37:39 AM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>01 Oct 2026 09:02:11 PM</t>
+          <t>02 Oct 2026 04:05:32 PM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 11:02:13 AM</t>
+          <t>03 Oct 2026 10:37:39 AM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -4720,19 +5504,19 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>1d 14h</t>
+          <t>18h 32m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1355782</t>
+          <t>TKT1354592</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>subesh puri</t>
+          <t>Santosh Shrestha</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -4762,22 +5546,22 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 10:53:31 AM</t>
+          <t>03 Oct 2026 11:02:13 AM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>02 Oct 2026 06:14:50 PM</t>
+          <t>01 Oct 2026 09:02:11 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 10:53:31 AM</t>
+          <t>03 Oct 2026 11:02:13 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -4787,19 +5571,19 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>16h 38m</t>
+          <t>1d 14h</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1354797</t>
+          <t>TKT1355782</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Shreyak Timsina</t>
+          <t>subesh puri</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -4829,22 +5613,22 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 11:13:21 AM</t>
+          <t>03 Oct 2026 10:53:31 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>02 Oct 2026 09:20:39 AM</t>
+          <t>02 Oct 2026 06:14:50 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 11:13:21 AM</t>
+          <t>03 Oct 2026 10:53:31 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -4854,19 +5638,19 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>1d 1h 52m</t>
+          <t>16h 38m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1356143</t>
+          <t>TKT1354797</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Pemchheku Sherpa</t>
+          <t>Shreyak Timsina</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -4896,22 +5680,22 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 11:37:04 AM</t>
+          <t>03 Oct 2026 11:13:21 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 08:10:26 AM</t>
+          <t>02 Oct 2026 09:20:39 AM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 11:37:04 AM</t>
+          <t>03 Oct 2026 11:13:21 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -4921,74 +5705,275 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>3h 26m</t>
+          <t>1d 1h 52m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
+          <t>TKT1356143</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Pemchheku Sherpa</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:37:04 AM</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 08:10:26 AM</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:37:04 AM</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>3h 26m</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
           <t>TKT1355761</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B32" s="3" t="inlineStr">
         <is>
           <t>Kabiraj Limbu</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C32" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr">
+      <c r="D32" s="3" t="inlineStr">
         <is>
           <t>Query For Secondary Router /Repeater</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F31" s="5" t="inlineStr">
+      <c r="F32" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>Case : secondary router connection  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>Case : secondary router connection  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="I32" s="3" t="inlineStr">
         <is>
           <t>03 Oct 2026 11:49:29 AM</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr">
+      <c r="J32" s="3" t="inlineStr">
         <is>
           <t>02 Oct 2026 05:58:41 PM</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="K32" s="3" t="inlineStr">
         <is>
           <t>03 Oct 2026 11:49:29 AM</t>
         </is>
       </c>
-      <c r="L31" s="5" t="inlineStr">
+      <c r="L32" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M31" s="5" t="inlineStr">
+      <c r="M32" s="3" t="inlineStr">
         <is>
           <t>17h 50m</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>TKT1355534</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Netra bahadur basnet</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:13:15 PM</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 03:42:55 PM</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:13:15 PM</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>20h 30m</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1354926</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Shreejan Shrestha</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 router   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:05:03 PM</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 10:25:56 AM</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:05:03 PM</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 39m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_03_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_03_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW23"/>
+  <dimension ref="A1:AW24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4081,10 +4081,8 @@
           <t>Parkas Nepal</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9849025416</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9849025416</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -4174,25 +4172,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
           <t>L62-4</t>
         </is>
       </c>
-      <c r="AP20" s="3" t="inlineStr">
-        <is>
-          <t>85.2867</t>
-        </is>
+      <c r="AP20" s="3" t="n">
+        <v>85.2867</v>
       </c>
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 upgrade  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
@@ -4288,10 +4282,8 @@
           <t>Saugat Kamal Upradi</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9808035363</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9808035363</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -4381,25 +4373,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>1,3</t>
         </is>
       </c>
-      <c r="AP21" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>Case : no internet  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
@@ -4495,10 +4483,8 @@
           <t>Netra bahadur basnet</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9849751248</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9849751248</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -4570,10 +4556,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH22" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH22" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI22" s="3" t="inlineStr">
         <is>
@@ -4592,10 +4576,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
@@ -4606,7 +4588,7 @@
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
@@ -4702,10 +4684,8 @@
           <t>Shreejan Shrestha</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9863229300</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9863229300</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -4799,50 +4779,253 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
           <t>2,1</t>
         </is>
       </c>
-      <c r="AP23" s="3" t="inlineStr">
-        <is>
-          <t>85.307746</t>
-        </is>
+      <c r="AP23" s="3" t="n">
+        <v>85.30774599999999</v>
       </c>
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 39m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6 router   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS23" s="3" t="inlineStr">
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:27 PM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : worst internet service   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>worst internet service</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350654</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Shrestha</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Shrestha</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9700971170</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:27:03 PM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>9823190890R</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 07:40:24 PM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:27:03 PM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>27.66368,</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr">
+        <is>
+          <t>Box End</t>
+        </is>
+      </c>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>ala Futsal &amp; Recreational Center Details from Google Maps Unnamed Road, M87P+5VQ, ?????????? 44700 +</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr">
+        <is>
+          <t>rs1460451@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr"/>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr"/>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>1,15</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>85.33794</t>
+        </is>
+      </c>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : worst internet service   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT23" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 39m</t>
-        </is>
-      </c>
-      <c r="AU23" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV23" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 router   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW23" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>4d 16h 46m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : worst internet service   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -4866,7 +5049,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4894,7 +5077,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -4915,7 +5098,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.8%</t>
         </is>
       </c>
     </row>
@@ -4998,7 +5181,7 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>0</v>
@@ -5139,7 +5322,7 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>0</v>
@@ -5876,7 +6059,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
@@ -5943,7 +6126,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_03_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_03_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW24"/>
+  <dimension ref="A1:AW26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -4889,10 +4889,8 @@
           <t>Roshan Shrestha</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9700971170</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9700971170</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -4982,50 +4980,460 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
           <t>1,15</t>
         </is>
       </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>85.33794</t>
-        </is>
+      <c r="AP24" s="3" t="n">
+        <v>85.33794</v>
       </c>
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>4d 16h 46m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
           <t>Case : worst internet service   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS24" s="3" t="inlineStr">
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:35 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355967</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Shashi kumar thakur</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Shashi kumar thakur</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9818217448</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:35:02 PM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>KLK9818217448</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 08:46:33 PM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:35:02 PM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr"/>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Goldhunga Orchid Academy Goldhunga Orchid Academy - School P7WW+JJ5 Kathmandu 44600, Kathmandu, Nepa</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr">
+        <is>
+          <t>9818217448@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>02:35 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>L58-2</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr"/>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT24" s="3" t="inlineStr">
-        <is>
-          <t>4d 16h 46m</t>
-        </is>
-      </c>
-      <c r="AU24" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV24" s="3" t="inlineStr">
-        <is>
-          <t>Case : worst internet service   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW24" s="3" t="inlineStr">
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>15h 48m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:45 PM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>For upgradation to wifi6</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355564</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Lil Bahadur Rokka</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Lil Bahadur Rokka</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>9841976019</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:45:23 PM</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>9841976019</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 04:02:07 PM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:45:23 PM</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t>27.69</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr">
+        <is>
+          <t>Near Suryamukhi Park, Kathmandu 44600 - Kathmandu Metropolitan, Kathmandu, Bagmati, Nepal, Nepal, Ba</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="inlineStr">
+        <is>
+          <t>lb19rokaha@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr">
+        <is>
+          <t>06:43 hour</t>
+        </is>
+      </c>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>L42-7</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr">
+        <is>
+          <t>85.3663</t>
+        </is>
+      </c>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>20h 43m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M34"/>
+  <dimension ref="A1:M36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -5049,7 +5457,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -5077,7 +5485,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -5087,7 +5495,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -5098,7 +5506,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>52.0%</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5530,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>20h 9m</t>
+          <t>19h 51m</t>
         </is>
       </c>
     </row>
@@ -5163,14 +5571,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>72.2%</t>
         </is>
       </c>
     </row>
@@ -5276,14 +5684,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>70.6%</t>
         </is>
       </c>
     </row>
@@ -6160,6 +6568,140 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>TKT1355967</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Shashi kumar thakur</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:35:02 PM</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 08:46:33 PM</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:35:02 PM</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>15h 48m</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355564</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Lil Bahadur Rokka</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:45:23 PM</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 04:02:07 PM</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:45:23 PM</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>20h 43m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_03_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_03_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW26"/>
+  <dimension ref="A1:AW29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5090,10 +5090,8 @@
           <t>Shashi kumar thakur</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9818217448</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9818217448</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -5183,10 +5181,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
@@ -5197,7 +5193,7 @@
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS25" s="3" t="inlineStr">
@@ -5293,10 +5289,8 @@
           <t>Lil Bahadur Rokka</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>9841976019</t>
-        </is>
+      <c r="O26" s="3" t="n">
+        <v>9841976019</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -5390,48 +5384,553 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN26" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
           <t>L42-7</t>
         </is>
       </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>85.3663</t>
-        </is>
+      <c r="AP26" s="3" t="n">
+        <v>85.3663</v>
       </c>
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>20h 43m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
           <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS26" s="3" t="inlineStr">
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:58 PM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355371</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Anmol Shah</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Anmol Shah</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9849940329</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:58:43 PM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>9748772741</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:09:56 PM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:58:43 PM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr"/>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>The Burger House And Crunchy Fried Chicken Sukedhara - Fast food restaurant Sukedhara Nilopul Road,,</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr">
+        <is>
+          <t>anmol123.as@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr">
+        <is>
+          <t>08:49 hour</t>
+        </is>
+      </c>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>L57-8</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr"/>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT26" s="3" t="inlineStr">
-        <is>
-          <t>20h 43m</t>
-        </is>
-      </c>
-      <c r="AU26" s="3" t="inlineStr">
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>22h 48m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV26" s="3" t="inlineStr">
-        <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW26" s="3" t="inlineStr">
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:47 PM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355371</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Anmol Shah</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Anmol Shah</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>9849940329</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:58:43 PM</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>9748772741</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:09:56 PM</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:58:43 PM</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr"/>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC28" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr">
+        <is>
+          <t>The Burger House And Crunchy Fried Chicken Sukedhara - Fast food restaurant Sukedhara Nilopul Road,,</t>
+        </is>
+      </c>
+      <c r="AF28" s="3" t="inlineStr">
+        <is>
+          <t>anmol123.as@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr">
+        <is>
+          <t>08:49 hour</t>
+        </is>
+      </c>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>L57-8</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr"/>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>22h 48m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:47 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr"/>
+      <c r="J29" s="3" t="inlineStr"/>
+      <c r="K29" s="3" t="inlineStr"/>
+      <c r="L29" s="3" t="inlineStr"/>
+      <c r="M29" s="3" t="inlineStr"/>
+      <c r="N29" s="3" t="inlineStr"/>
+      <c r="O29" s="3" t="inlineStr"/>
+      <c r="P29" s="3" t="inlineStr"/>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr"/>
+      <c r="S29" s="3" t="inlineStr"/>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr"/>
+      <c r="V29" s="3" t="inlineStr"/>
+      <c r="W29" s="3" t="inlineStr"/>
+      <c r="X29" s="3" t="inlineStr"/>
+      <c r="Y29" s="3" t="inlineStr"/>
+      <c r="Z29" s="3" t="inlineStr"/>
+      <c r="AA29" s="3" t="inlineStr"/>
+      <c r="AB29" s="3" t="inlineStr"/>
+      <c r="AC29" s="3" t="inlineStr"/>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr"/>
+      <c r="AF29" s="3" t="inlineStr"/>
+      <c r="AG29" s="3" t="inlineStr"/>
+      <c r="AH29" s="3" t="inlineStr"/>
+      <c r="AI29" s="3" t="inlineStr"/>
+      <c r="AJ29" s="3" t="inlineStr"/>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr"/>
+      <c r="AM29" s="3" t="inlineStr"/>
+      <c r="AN29" s="3" t="inlineStr"/>
+      <c r="AO29" s="3" t="inlineStr"/>
+      <c r="AP29" s="3" t="inlineStr"/>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -5448,7 +5947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M36"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -5485,7 +5984,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -5495,7 +5994,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -5506,7 +6005,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>53.6%</t>
         </is>
       </c>
     </row>
@@ -5530,7 +6029,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>19h 51m</t>
+          <t>20h 15m</t>
         </is>
       </c>
     </row>
@@ -5571,14 +6070,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -5684,14 +6183,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>73.7%</t>
         </is>
       </c>
     </row>
@@ -6601,7 +7100,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
@@ -6668,14 +7167,14 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
           <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
           <t>03 Oct 2026 12:45:23 PM</t>
@@ -6699,6 +7198,140 @@
       <c r="M36" s="3" t="inlineStr">
         <is>
           <t>20h 43m</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>TKT1355371</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Anmol Shah</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:58:43 PM</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:09:56 PM</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:58:43 PM</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>22h 48m</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355371</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>Anmol Shah</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:58:43 PM</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:09:56 PM</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 12:58:43 PM</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>22h 48m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_03_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_03_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW29"/>
+  <dimension ref="A1:AW31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5494,10 +5494,8 @@
           <t>Anmol Shah</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9849940329</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9849940329</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -5587,10 +5585,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
@@ -5601,7 +5597,7 @@
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
@@ -5697,10 +5693,8 @@
           <t>Anmol Shah</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>9849940329</t>
-        </is>
+      <c r="O28" s="3" t="n">
+        <v>9849940329</v>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
@@ -5790,10 +5784,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN28" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
@@ -5804,7 +5796,7 @@
       <c r="AQ28" s="3" t="inlineStr"/>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
@@ -5936,6 +5928,412 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 1:04 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355468</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Jhalak Devi Bhandari</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Jhalak Devi Bhandari</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>9803600675</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 01:04:25 PM</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>CHB9803600675</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:57:40 PM</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 01:04:25 PM</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr"/>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>METRO MARKET - Market M8RW+45Q Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr">
+        <is>
+          <t>test@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr">
+        <is>
+          <t>08:07 hour</t>
+        </is>
+      </c>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>L25-8</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr"/>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>22h 6m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 1:03 PM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355468</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Jhalak Devi Bhandari</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Jhalak Devi Bhandari</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>9803600675</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 01:04:25 PM</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>CHB9803600675</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:57:40 PM</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 01:04:25 PM</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr"/>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>METRO MARKET - Market M8RW+45Q Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr">
+        <is>
+          <t>test@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG31" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr">
+        <is>
+          <t>08:07 hour</t>
+        </is>
+      </c>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>L25-8</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr"/>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>22h 6m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5947,7 +6345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -5984,7 +6382,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -5994,7 +6392,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -6005,7 +6403,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>56.7%</t>
         </is>
       </c>
     </row>
@@ -6029,7 +6427,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>20h 15m</t>
+          <t>20h 28m</t>
         </is>
       </c>
     </row>
@@ -6070,14 +6468,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.3%</t>
         </is>
       </c>
     </row>
@@ -6183,14 +6581,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>76.2%</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7632,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
@@ -7301,14 +7699,14 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
           <t>Case : WIFI6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>Case : WIFI6   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
           <t>03 Oct 2026 12:58:43 PM</t>
@@ -7332,6 +7730,140 @@
       <c r="M38" s="3" t="inlineStr">
         <is>
           <t>22h 48m</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>TKT1355468</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Jhalak Devi Bhandari</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 01:04:25 PM</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:57:40 PM</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 01:04:25 PM</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>22h 6m</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355468</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>Jhalak Devi Bhandari</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 01:04:25 PM</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:57:40 PM</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 01:04:25 PM</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>22h 6m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_03_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_03_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW31"/>
+  <dimension ref="A1:AW32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -5995,10 +5995,8 @@
           <t>Jhalak Devi Bhandari</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>9803600675</t>
-        </is>
+      <c r="O30" s="3" t="n">
+        <v>9803600675</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -6088,10 +6086,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN30" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
@@ -6102,7 +6098,7 @@
       <c r="AQ30" s="3" t="inlineStr"/>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
@@ -6198,10 +6194,8 @@
           <t>Jhalak Devi Bhandari</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>9803600675</t>
-        </is>
+      <c r="O31" s="3" t="n">
+        <v>9803600675</v>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
@@ -6291,10 +6285,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN31" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
@@ -6305,30 +6297,233 @@
       <c r="AQ31" s="3" t="inlineStr"/>
       <c r="AR31" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>22h 6m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
           <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS31" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT31" s="3" t="inlineStr">
-        <is>
-          <t>22h 6m</t>
-        </is>
-      </c>
-      <c r="AU31" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV31" s="3" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 1:18 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>For upgradation to wifi6</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355876</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Kamal Khatri</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Kamal Khatri</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9702617283</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 07:38:32 PM</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>BKT9702617283</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 07:38:32 PM</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 01:18:36 PM</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr"/>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>Suryabinayak Chowk near Ganesh mandir , Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr">
+        <is>
+          <t>9861283872@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI32" s="3" t="inlineStr"/>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>3,3</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr"/>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>17h 40m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>17h 40m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -6354,7 +6549,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -6382,7 +6577,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
@@ -6403,7 +6598,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
     </row>
@@ -6468,14 +6663,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>17</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>73.9%</t>
         </is>
       </c>
     </row>
@@ -6581,14 +6776,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D17" s="5" t="n">
         <v>16</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -7766,7 +7961,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
@@ -7833,7 +8028,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_03_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_03_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW32"/>
+  <dimension ref="A1:AW33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -6393,10 +6393,8 @@
           <t>Kamal Khatri</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>9702617283</t>
-        </is>
+      <c r="O32" s="3" t="n">
+        <v>9702617283</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -6468,10 +6466,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH32" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH32" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI32" s="3" t="inlineStr"/>
       <c r="AJ32" s="3" t="inlineStr"/>
@@ -6486,10 +6482,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN32" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
@@ -6500,30 +6494,133 @@
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>17h 40m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>17h 40m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
           <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS32" s="3" t="inlineStr">
-        <is>
-          <t>17h 40m</t>
-        </is>
-      </c>
-      <c r="AT32" s="3" t="inlineStr">
-        <is>
-          <t>17h 40m</t>
-        </is>
-      </c>
-      <c r="AU32" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV32" s="3" t="inlineStr">
-        <is>
-          <t>Case : For upgradation to wifi6   has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 1:22 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 connect  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr"/>
+      <c r="J33" s="3" t="inlineStr"/>
+      <c r="K33" s="3" t="inlineStr"/>
+      <c r="L33" s="3" t="inlineStr"/>
+      <c r="M33" s="3" t="inlineStr"/>
+      <c r="N33" s="3" t="inlineStr"/>
+      <c r="O33" s="3" t="inlineStr"/>
+      <c r="P33" s="3" t="inlineStr"/>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr"/>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr"/>
+      <c r="V33" s="3" t="inlineStr"/>
+      <c r="W33" s="3" t="inlineStr"/>
+      <c r="X33" s="3" t="inlineStr"/>
+      <c r="Y33" s="3" t="inlineStr"/>
+      <c r="Z33" s="3" t="inlineStr"/>
+      <c r="AA33" s="3" t="inlineStr"/>
+      <c r="AB33" s="3" t="inlineStr"/>
+      <c r="AC33" s="3" t="inlineStr"/>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr"/>
+      <c r="AF33" s="3" t="inlineStr"/>
+      <c r="AG33" s="3" t="inlineStr"/>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr"/>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr"/>
+      <c r="AM33" s="3" t="inlineStr"/>
+      <c r="AN33" s="3" t="inlineStr"/>
+      <c r="AO33" s="3" t="inlineStr"/>
+      <c r="AP33" s="3" t="inlineStr"/>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 connect  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -6577,7 +6674,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -6598,7 +6695,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>53.1%</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_03_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_03_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW33"/>
+  <dimension ref="A1:AW34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -6626,6 +6626,109 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 1:35 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr"/>
+      <c r="J34" s="3" t="inlineStr"/>
+      <c r="K34" s="3" t="inlineStr"/>
+      <c r="L34" s="3" t="inlineStr"/>
+      <c r="M34" s="3" t="inlineStr"/>
+      <c r="N34" s="3" t="inlineStr"/>
+      <c r="O34" s="3" t="inlineStr"/>
+      <c r="P34" s="3" t="inlineStr"/>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr"/>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr"/>
+      <c r="V34" s="3" t="inlineStr"/>
+      <c r="W34" s="3" t="inlineStr"/>
+      <c r="X34" s="3" t="inlineStr"/>
+      <c r="Y34" s="3" t="inlineStr"/>
+      <c r="Z34" s="3" t="inlineStr"/>
+      <c r="AA34" s="3" t="inlineStr"/>
+      <c r="AB34" s="3" t="inlineStr"/>
+      <c r="AC34" s="3" t="inlineStr"/>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr"/>
+      <c r="AF34" s="3" t="inlineStr"/>
+      <c r="AG34" s="3" t="inlineStr"/>
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="3" t="inlineStr"/>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr"/>
+      <c r="AM34" s="3" t="inlineStr"/>
+      <c r="AN34" s="3" t="inlineStr"/>
+      <c r="AO34" s="3" t="inlineStr"/>
+      <c r="AP34" s="3" t="inlineStr"/>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6674,7 +6777,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3">
@@ -6695,7 +6798,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>51.5%</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_03_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_03_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW34"/>
+  <dimension ref="A1:AW39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -523,13 +523,13 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -6729,6 +6729,1049 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 2:03 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>For upgradation to wifi6</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355502</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Ambika Dahal</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>Ambika Dahal</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>9808261915</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 03:19:58 PM</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>9803899927</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 03:19:58 PM</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:03:46 PM</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr">
+        <is>
+          <t>27.73524</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC35" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>Gongabu near yeti guest house, terathum chitwan guest house, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr">
+        <is>
+          <t>heavenqueen9595@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG35" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="3" t="inlineStr">
+        <is>
+          <t>08:44 hour</t>
+        </is>
+      </c>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>Pradeep Yadav</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>L48-8</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr">
+        <is>
+          <t>85.3092</t>
+        </is>
+      </c>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>22h 43m</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>22h 43m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 2:06 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1356128</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Tamang</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Tamang</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>9851014734</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:06:04 PM</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>9851014734</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 07:53:56 AM</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:06:04 PM</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t>27.716612</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>Lords Light Academy (LLA) - School 44604 Kathmandu 44604 , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
+        <is>
+          <t>bajrasatwo@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr">
+        <is>
+          <t>04:06 hour</t>
+        </is>
+      </c>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>L49-8</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>85.364232</t>
+        </is>
+      </c>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>6h 12m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 2:15 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1356156</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>Mahesh Dahal</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>Mahesh Dahal</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9864002642</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 08:35:35 AM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>9864002642</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 08:35:35 AM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:15:25 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr">
+        <is>
+          <t>27.66586</t>
+        </is>
+      </c>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>M983+W75, Mahalaxmi 44600 near by Bhagwati Mandir, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr">
+        <is>
+          <t>mahesh.mandk@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr"/>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>CDB527</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr">
+        <is>
+          <t>85.35689</t>
+        </is>
+      </c>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>5h 39m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>5h 39m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 2:11 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1356156</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Mahesh Dahal</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Mahesh Dahal</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>9864002642</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 08:35:35 AM</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>9864002642</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 08:35:35 AM</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:15:25 PM</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr">
+        <is>
+          <t>27.66586</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA38" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC38" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr">
+        <is>
+          <t>M983+W75, Mahalaxmi 44600 near by Bhagwati Mandir, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr">
+        <is>
+          <t>mahesh.mandk@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="3" t="inlineStr"/>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>CDB527</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr">
+        <is>
+          <t>85.35689</t>
+        </is>
+      </c>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>5h 39m</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>5h 39m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 2:02 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355548</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Sadhuram Baniya</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>Sadhuram Baniya</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>9841475616</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:02:00 PM</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>9841475616</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 03:53:00 PM</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:02:00 PM</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t>27.649157</t>
+        </is>
+      </c>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA39" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC39" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr">
+        <is>
+          <t>Mahalaxmi Municipality -7, Changathali, Lalitpur, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="inlineStr"/>
+      <c r="AG39" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr">
+        <is>
+          <t>08:09 hour</t>
+        </is>
+      </c>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>L62-5</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr">
+        <is>
+          <t>85.367026</t>
+        </is>
+      </c>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>22h 9m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6740,7 +7783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -6749,7 +7792,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -6777,7 +7820,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3">
@@ -6787,7 +7830,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -6798,7 +7841,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>52.6%</t>
         </is>
       </c>
     </row>
@@ -6810,7 +7853,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>1h 8m</t>
         </is>
       </c>
     </row>
@@ -6822,7 +7865,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>20h 28m</t>
+          <t>19h 57m</t>
         </is>
       </c>
     </row>
@@ -6863,14 +7906,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -6976,14 +8019,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>70.4%</t>
         </is>
       </c>
     </row>
@@ -8262,6 +9305,207 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>TKT1355502</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Ambika Dahal</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 03:19:58 PM</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 03:19:58 PM</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:03:46 PM</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>22h 43m</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>22h 43m</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1356128</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Tamang</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:06:04 PM</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 07:53:56 AM</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:06:04 PM</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>6h 12m</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>TKT1355548</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Sadhuram Baniya</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:02:00 PM</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 03:53:00 PM</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:02:00 PM</t>
+        </is>
+      </c>
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>22h 9m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_03_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_03_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW39"/>
+  <dimension ref="A1:AW40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -6796,10 +6796,8 @@
           <t>Ambika Dahal</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>9808261915</t>
-        </is>
+      <c r="O35" s="3" t="n">
+        <v>9808261915</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
@@ -6893,25 +6891,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN35" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
           <t>L48-8</t>
         </is>
       </c>
-      <c r="AP35" s="3" t="inlineStr">
-        <is>
-          <t>85.3092</t>
-        </is>
+      <c r="AP35" s="3" t="n">
+        <v>85.3092</v>
       </c>
       <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS35" s="3" t="inlineStr">
@@ -7007,10 +7001,8 @@
           <t>Sunita Tamang</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>9851014734</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>9851014734</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -7104,25 +7096,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN36" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
           <t>L49-8</t>
         </is>
       </c>
-      <c r="AP36" s="3" t="inlineStr">
-        <is>
-          <t>85.364232</t>
-        </is>
+      <c r="AP36" s="3" t="n">
+        <v>85.364232</v>
       </c>
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS36" s="3" t="inlineStr">
@@ -7218,10 +7206,8 @@
           <t>Mahesh Dahal</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9864002642</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9864002642</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -7311,25 +7297,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
           <t>CDB527</t>
         </is>
       </c>
-      <c r="AP37" s="3" t="inlineStr">
-        <is>
-          <t>85.35689</t>
-        </is>
+      <c r="AP37" s="3" t="n">
+        <v>85.35689000000001</v>
       </c>
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
@@ -7425,10 +7407,8 @@
           <t>Mahesh Dahal</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>9864002642</t>
-        </is>
+      <c r="O38" s="3" t="n">
+        <v>9864002642</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
@@ -7518,25 +7498,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN38" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
           <t>CDB527</t>
         </is>
       </c>
-      <c r="AP38" s="3" t="inlineStr">
-        <is>
-          <t>85.35689</t>
-        </is>
+      <c r="AP38" s="3" t="n">
+        <v>85.35689000000001</v>
       </c>
       <c r="AQ38" s="3" t="inlineStr"/>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
@@ -7632,10 +7608,8 @@
           <t>Sadhuram Baniya</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>9841475616</t>
-        </is>
+      <c r="O39" s="3" t="n">
+        <v>9841475616</v>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
@@ -7725,48 +7699,243 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN39" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
           <t>L62-5</t>
         </is>
       </c>
-      <c r="AP39" s="3" t="inlineStr">
-        <is>
-          <t>85.367026</t>
-        </is>
+      <c r="AP39" s="3" t="n">
+        <v>85.367026</v>
       </c>
       <c r="AQ39" s="3" t="inlineStr"/>
       <c r="AR39" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>22h 9m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS39" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT39" s="3" t="inlineStr">
-        <is>
-          <t>22h 9m</t>
-        </is>
-      </c>
-      <c r="AU39" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV39" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 2:30 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355348</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Sara korean mart</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Sara korean mart</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>9840738460</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:02:16 PM</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>9840738460</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:02:16 PM</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:30:41 PM</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr"/>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA40" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB40" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC40" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr">
+        <is>
+          <t>Sara Mart Details from Google Maps Unnamed Road, Kathmandu 44600, ???????? 44600 www.instagram.com +</t>
+        </is>
+      </c>
+      <c r="AF40" s="3" t="inlineStr"/>
+      <c r="AG40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH40" s="3" t="inlineStr"/>
+      <c r="AI40" s="3" t="inlineStr">
+        <is>
+          <t>10:28 hour</t>
+        </is>
+      </c>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO40" s="3" t="inlineStr">
+        <is>
+          <t>L43-2</t>
+        </is>
+      </c>
+      <c r="AP40" s="3" t="inlineStr"/>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>1d 28m</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>1d 28m</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -7783,7 +7952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -7820,7 +7989,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3">
@@ -7830,7 +7999,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -7841,7 +8010,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>53.8%</t>
         </is>
       </c>
     </row>
@@ -7853,7 +8022,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>1h 8m</t>
+          <t>2h 14m</t>
         </is>
       </c>
     </row>
@@ -7865,7 +8034,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>19h 57m</t>
+          <t>20h 10m</t>
         </is>
       </c>
     </row>
@@ -7906,14 +8075,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>72.4%</t>
         </is>
       </c>
     </row>
@@ -8019,14 +8188,14 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -9338,7 +9507,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
@@ -9405,7 +9574,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
@@ -9472,14 +9641,14 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
           <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
           <t>03 Oct 2026 02:02:00 PM</t>
@@ -9503,6 +9672,73 @@
       <c r="M43" s="5" t="inlineStr">
         <is>
           <t>22h 9m</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355348</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Sara korean mart</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:02:16 PM</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 02:02:16 PM</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:30:41 PM</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>1d 28m</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>1d 28m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_03_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_03_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -7809,10 +7809,8 @@
           <t>Sara korean mart</t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>9840738460</t>
-        </is>
+      <c r="O40" s="3" t="n">
+        <v>9840738460</v>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
@@ -7898,10 +7896,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN40" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
@@ -7912,7 +7908,7 @@
       <c r="AQ40" s="3" t="inlineStr"/>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
@@ -7961,7 +7957,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -9708,7 +9704,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_03_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_03_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW40"/>
+  <dimension ref="A1:AW42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -501,7 +501,7 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="28" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="27" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -511,7 +511,7 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="27" customWidth="1" min="26" max="26"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
     <col width="24" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -7937,6 +7937,436 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 3:12 PM</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router replacement   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>Router replacement</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355100</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Himmat  Shrestha</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Himmat  Shrestha</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>9847898946</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:09:15 PM</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>9847898946</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 12:26:56 PM</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 03:12:22 PM</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t>27.72241</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA41" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB41" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC41" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD41" s="3" t="inlineStr"/>
+      <c r="AE41" s="3" t="inlineStr">
+        <is>
+          <t>P895+JVQ, Kathmandu 44600 near by Agassi_collection, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF41" s="3" t="inlineStr">
+        <is>
+          <t>himmatshrestha98@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG41" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH41" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI41" s="3" t="inlineStr">
+        <is>
+          <t>12:45 hour</t>
+        </is>
+      </c>
+      <c r="AJ41" s="3" t="inlineStr"/>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>CDB075</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>85.31133</t>
+        </is>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr"/>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router replacement   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>1h 3m</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 45m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router replacement   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 3:11 PM</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router replacement   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>Router replacement</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355100</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>Himmat  Shrestha</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Himmat  Shrestha</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>9847898946</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:09:15 PM</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>9847898946</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 12:26:56 PM</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 03:12:22 PM</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr">
+        <is>
+          <t>27.72241</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA42" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB42" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC42" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="inlineStr"/>
+      <c r="AE42" s="3" t="inlineStr">
+        <is>
+          <t>P895+JVQ, Kathmandu 44600 near by Agassi_collection, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF42" s="3" t="inlineStr">
+        <is>
+          <t>himmatshrestha98@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG42" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH42" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI42" s="3" t="inlineStr">
+        <is>
+          <t>12:45 hour</t>
+        </is>
+      </c>
+      <c r="AJ42" s="3" t="inlineStr"/>
+      <c r="AK42" s="3" t="inlineStr"/>
+      <c r="AL42" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>CDB075</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr">
+        <is>
+          <t>85.31133</t>
+        </is>
+      </c>
+      <c r="AQ42" s="3" t="inlineStr"/>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router replacement   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>1h 3m</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 45m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router replacement   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7948,16 +8378,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -7985,7 +8415,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3">
@@ -7995,7 +8425,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
@@ -8006,7 +8436,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>56.1%</t>
         </is>
       </c>
     </row>
@@ -8018,7 +8448,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2h 14m</t>
+          <t>2h 8m</t>
         </is>
       </c>
     </row>
@@ -8030,7 +8460,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>20h 10m</t>
+          <t>20h 44m</t>
         </is>
       </c>
     </row>
@@ -8085,90 +8515,85 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr"/>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr"/>
+      <c r="B13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Total Scraped Tickets</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>Solved / Handled Count</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Query For Secondary Router /Repeater</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Total Scraped Tickets</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Solved / Handled Count</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Solution Rate %</t>
         </is>
       </c>
     </row>
@@ -8180,300 +8605,212 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Query For Secondary Router /Repeater</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Specific Website/App is slow</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Slow Internet Connection</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr"/>
-      <c r="B20" s="3" t="inlineStr"/>
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Specific Website/App is slow</t>
+        </is>
+      </c>
       <c r="C20" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
           <t>nan%</t>
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Ticket Number</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Account Name</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
-        <is>
-          <t>Sub Category</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Type</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>Employee Remark / Solution Note</t>
-        </is>
-      </c>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Action / Transfer Remark</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>Assigned Date</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>Created Date</t>
-        </is>
-      </c>
-      <c r="K23" s="4" t="inlineStr">
-        <is>
-          <t>Last Modified Date</t>
-        </is>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Assigned)</t>
-        </is>
-      </c>
-      <c r="M23" s="4" t="inlineStr">
-        <is>
-          <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>TKT1355412</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Mukunda  Prasad Khatiwada</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>03 Oct 2026 09:56:56 AM</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>02 Oct 2026 02:26:17 PM</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>03 Oct 2026 09:56:56 AM</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>19h 30m</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TKT1355678</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>sabita karki</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>03 Oct 2026 10:20:27 AM</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>02 Oct 2026 05:14:25 PM</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>03 Oct 2026 10:20:27 AM</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>17h 6m</t>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Ticket Number</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Account Name</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Sub Category</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Type</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Employee Remark / Solution Note</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Action / Transfer Remark</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>Assigned Date</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>Created Date</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>Last Modified Date</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Assigned)</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1355553</t>
+          <t>TKT1355412</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Santosh Khatiwada</t>
+          <t>Mukunda  Prasad Khatiwada</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -8503,22 +8840,22 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+          <t>Case : Router Upgrade   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 10:30:57 AM</t>
+          <t>03 Oct 2026 09:56:56 AM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>02 Oct 2026 03:55:48 PM</t>
+          <t>02 Oct 2026 02:26:17 PM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 10:30:57 AM</t>
+          <t>03 Oct 2026 09:56:56 AM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -8528,19 +8865,19 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>18h 35m</t>
+          <t>19h 30m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1355571</t>
+          <t>TKT1355678</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Puran  Kumar shrestha</t>
+          <t>sabita karki</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
@@ -8570,22 +8907,22 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 10:37:39 AM</t>
+          <t>03 Oct 2026 10:20:27 AM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>02 Oct 2026 04:05:32 PM</t>
+          <t>02 Oct 2026 05:14:25 PM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 10:37:39 AM</t>
+          <t>03 Oct 2026 10:20:27 AM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -8595,19 +8932,19 @@
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>18h 32m</t>
+          <t>17h 6m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1354592</t>
+          <t>TKT1355553</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Santosh Shrestha</t>
+          <t>Santosh Khatiwada</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -8637,22 +8974,22 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 11:02:13 AM</t>
+          <t>03 Oct 2026 10:30:57 AM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>01 Oct 2026 09:02:11 PM</t>
+          <t>02 Oct 2026 03:55:48 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 11:02:13 AM</t>
+          <t>03 Oct 2026 10:30:57 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -8662,19 +8999,19 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>1d 14h</t>
+          <t>18h 35m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1355782</t>
+          <t>TKT1355571</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>subesh puri</t>
+          <t>Puran  Kumar shrestha</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -8704,22 +9041,22 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 10:53:31 AM</t>
+          <t>03 Oct 2026 10:37:39 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>02 Oct 2026 06:14:50 PM</t>
+          <t>02 Oct 2026 04:05:32 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 10:53:31 AM</t>
+          <t>03 Oct 2026 10:37:39 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -8729,19 +9066,19 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>16h 38m</t>
+          <t>18h 32m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1354797</t>
+          <t>TKT1354592</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Shreyak Timsina</t>
+          <t>Santosh Shrestha</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -8771,22 +9108,22 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>Case : WiFi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 11:13:21 AM</t>
+          <t>03 Oct 2026 11:02:13 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>02 Oct 2026 09:20:39 AM</t>
+          <t>01 Oct 2026 09:02:11 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 11:13:21 AM</t>
+          <t>03 Oct 2026 11:02:13 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -8796,19 +9133,19 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 52m</t>
+          <t>1d 14h</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1356143</t>
+          <t>TKT1355782</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Pemchheku Sherpa</t>
+          <t>subesh puri</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -8838,22 +9175,22 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 11:37:04 AM</t>
+          <t>03 Oct 2026 10:53:31 AM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 08:10:26 AM</t>
+          <t>02 Oct 2026 06:14:50 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 11:37:04 AM</t>
+          <t>03 Oct 2026 10:53:31 AM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
@@ -8863,19 +9200,19 @@
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>3h 26m</t>
+          <t>16h 38m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1355761</t>
+          <t>TKT1354797</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Kabiraj Limbu</t>
+          <t>Shreyak Timsina</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -8885,7 +9222,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>Query For Secondary Router /Repeater</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -8905,22 +9242,22 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : secondary router connection  has been updated by Sabin Giri</t>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 11:49:29 AM</t>
+          <t>03 Oct 2026 11:13:21 AM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>02 Oct 2026 05:58:41 PM</t>
+          <t>02 Oct 2026 09:20:39 AM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 11:49:29 AM</t>
+          <t>03 Oct 2026 11:13:21 AM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
@@ -8930,19 +9267,19 @@
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>17h 50m</t>
+          <t>1d 1h 52m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1355534</t>
+          <t>TKT1356143</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Netra bahadur basnet</t>
+          <t>Pemchheku Sherpa</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -8972,22 +9309,22 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Sabin Giri</t>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 12:13:15 PM</t>
+          <t>03 Oct 2026 11:37:04 AM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>02 Oct 2026 03:42:55 PM</t>
+          <t>03 Oct 2026 08:10:26 AM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 12:13:15 PM</t>
+          <t>03 Oct 2026 11:37:04 AM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
@@ -8997,19 +9334,19 @@
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>20h 30m</t>
+          <t>3h 26m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1354926</t>
+          <t>TKT1355761</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Shreejan Shrestha</t>
+          <t>Kabiraj Limbu</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -9019,7 +9356,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Query For Secondary Router /Repeater</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -9039,22 +9376,22 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 router   has been updated by Chandramani Tharu</t>
+          <t>Case : secondary router connection  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 12:05:03 PM</t>
+          <t>03 Oct 2026 11:49:29 AM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>02 Oct 2026 10:25:56 AM</t>
+          <t>02 Oct 2026 05:58:41 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 12:05:03 PM</t>
+          <t>03 Oct 2026 11:49:29 AM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
@@ -9064,19 +9401,19 @@
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 39m</t>
+          <t>17h 50m</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>TKT1355967</t>
+          <t>TKT1355534</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Shashi kumar thakur</t>
+          <t>Netra bahadur basnet</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -9106,22 +9443,22 @@
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
+          <t>Case : WIFI 6  has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 12:35:02 PM</t>
+          <t>03 Oct 2026 12:13:15 PM</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>02 Oct 2026 08:46:33 PM</t>
+          <t>02 Oct 2026 03:42:55 PM</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 12:35:02 PM</t>
+          <t>03 Oct 2026 12:13:15 PM</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
@@ -9131,19 +9468,19 @@
       </c>
       <c r="M35" s="5" t="inlineStr">
         <is>
-          <t>15h 48m</t>
+          <t>20h 30m</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>TKT1355564</t>
+          <t>TKT1354926</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Lil Bahadur Rokka</t>
+          <t>Shreejan Shrestha</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -9173,22 +9510,22 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
+          <t>Case : wifi 6 router   has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 12:45:23 PM</t>
+          <t>03 Oct 2026 12:05:03 PM</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t>02 Oct 2026 04:02:07 PM</t>
+          <t>02 Oct 2026 10:25:56 AM</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 12:45:23 PM</t>
+          <t>03 Oct 2026 12:05:03 PM</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
@@ -9198,19 +9535,19 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>20h 43m</t>
+          <t>1d 1h 39m</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>TKT1355371</t>
+          <t>TKT1355967</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Anmol Shah</t>
+          <t>Shashi kumar thakur</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -9240,22 +9577,22 @@
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
+          <t>Case : WiFi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 12:58:43 PM</t>
+          <t>03 Oct 2026 12:35:02 PM</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>02 Oct 2026 02:09:56 PM</t>
+          <t>02 Oct 2026 08:46:33 PM</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 12:58:43 PM</t>
+          <t>03 Oct 2026 12:35:02 PM</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
@@ -9265,19 +9602,19 @@
       </c>
       <c r="M37" s="5" t="inlineStr">
         <is>
-          <t>22h 48m</t>
+          <t>15h 48m</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>TKT1355371</t>
+          <t>TKT1355564</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Anmol Shah</t>
+          <t>Lil Bahadur Rokka</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -9307,22 +9644,22 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6   has been updated by Sanjeev Giri</t>
+          <t>Case : For upgradation to wifi6   has been updated by Sabin Giri</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 12:58:43 PM</t>
+          <t>03 Oct 2026 12:45:23 PM</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>02 Oct 2026 02:09:56 PM</t>
+          <t>02 Oct 2026 04:02:07 PM</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 12:58:43 PM</t>
+          <t>03 Oct 2026 12:45:23 PM</t>
         </is>
       </c>
       <c r="L38" s="3" t="inlineStr">
@@ -9332,19 +9669,19 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>22h 48m</t>
+          <t>20h 43m</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>TKT1355468</t>
+          <t>TKT1355371</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Jhalak Devi Bhandari</t>
+          <t>Anmol Shah</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -9374,22 +9711,22 @@
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : Router Upgrade   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 01:04:25 PM</t>
+          <t>03 Oct 2026 12:58:43 PM</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>02 Oct 2026 02:57:40 PM</t>
+          <t>02 Oct 2026 02:09:56 PM</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 01:04:25 PM</t>
+          <t>03 Oct 2026 12:58:43 PM</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
@@ -9399,19 +9736,19 @@
       </c>
       <c r="M39" s="5" t="inlineStr">
         <is>
-          <t>22h 6m</t>
+          <t>22h 48m</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TKT1355468</t>
+          <t>TKT1355371</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Jhalak Devi Bhandari</t>
+          <t>Anmol Shah</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -9441,22 +9778,22 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
+          <t>Case : WIFI6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 01:04:25 PM</t>
+          <t>03 Oct 2026 12:58:43 PM</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t>02 Oct 2026 02:57:40 PM</t>
+          <t>02 Oct 2026 02:09:56 PM</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 01:04:25 PM</t>
+          <t>03 Oct 2026 12:58:43 PM</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
@@ -9466,19 +9803,19 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>22h 6m</t>
+          <t>22h 48m</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>TKT1355502</t>
+          <t>TKT1355468</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Ambika Dahal</t>
+          <t>Jhalak Devi Bhandari</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -9493,12 +9830,12 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -9508,44 +9845,44 @@
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>02 Oct 2026 03:19:58 PM</t>
+          <t>03 Oct 2026 01:04:25 PM</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>02 Oct 2026 03:19:58 PM</t>
+          <t>02 Oct 2026 02:57:40 PM</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 02:03:46 PM</t>
+          <t>03 Oct 2026 01:04:25 PM</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>22h 43m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M41" s="5" t="inlineStr">
         <is>
-          <t>22h 43m</t>
+          <t>22h 6m</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TKT1356128</t>
+          <t>TKT1355468</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Sunita Tamang</t>
+          <t>Jhalak Devi Bhandari</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -9575,22 +9912,22 @@
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>Case : WiFi 6  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 02:06:04 PM</t>
+          <t>03 Oct 2026 01:04:25 PM</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 07:53:56 AM</t>
+          <t>02 Oct 2026 02:57:40 PM</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>03 Oct 2026 02:06:04 PM</t>
+          <t>03 Oct 2026 01:04:25 PM</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
@@ -9600,19 +9937,19 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>6h 12m</t>
+          <t>22h 6m</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>TKT1355548</t>
+          <t>TKT1355502</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Sadhuram Baniya</t>
+          <t>Ambika Dahal</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -9627,12 +9964,12 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
@@ -9642,99 +9979,367 @@
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>Case : For upgradation to wifi6   has been updated by Ajit Shrestha</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 02:02:00 PM</t>
+          <t>02 Oct 2026 03:19:58 PM</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>02 Oct 2026 03:53:00 PM</t>
+          <t>02 Oct 2026 03:19:58 PM</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>03 Oct 2026 02:02:00 PM</t>
+          <t>03 Oct 2026 02:03:46 PM</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>22h 43m</t>
         </is>
       </c>
       <c r="M43" s="5" t="inlineStr">
         <is>
-          <t>22h 9m</t>
+          <t>22h 43m</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
+          <t>TKT1356128</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Tamang</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:06:04 PM</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 07:53:56 AM</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:06:04 PM</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>6h 12m</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>TKT1355548</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Sadhuram Baniya</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:02:00 PM</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 03:53:00 PM</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:02:00 PM</t>
+        </is>
+      </c>
+      <c r="L45" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>22h 9m</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
           <t>TKT1355348</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>Sara korean mart</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G44" s="3" t="inlineStr">
+      <c r="G46" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H44" s="3" t="inlineStr">
+      <c r="H46" s="3" t="inlineStr">
         <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr">
+      <c r="I46" s="3" t="inlineStr">
         <is>
           <t>02 Oct 2026 02:02:16 PM</t>
         </is>
       </c>
-      <c r="J44" s="3" t="inlineStr">
+      <c r="J46" s="3" t="inlineStr">
         <is>
           <t>02 Oct 2026 02:02:16 PM</t>
         </is>
       </c>
-      <c r="K44" s="3" t="inlineStr">
+      <c r="K46" s="3" t="inlineStr">
         <is>
           <t>03 Oct 2026 02:30:41 PM</t>
         </is>
       </c>
-      <c r="L44" s="3" t="inlineStr">
+      <c r="L46" s="3" t="inlineStr">
         <is>
           <t>1d 28m</t>
         </is>
       </c>
-      <c r="M44" s="3" t="inlineStr">
+      <c r="M46" s="3" t="inlineStr">
         <is>
           <t>1d 28m</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>TKT1355100</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Himmat  Shrestha</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router replacement   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router replacement   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:09:15 PM</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 12:26:56 PM</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 03:12:22 PM</t>
+        </is>
+      </c>
+      <c r="L47" s="5" t="inlineStr">
+        <is>
+          <t>1h 3m</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>1d 2h 45m</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>TKT1355100</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Himmat  Shrestha</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router replacement   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router replacement   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 02:09:15 PM</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>02 Oct 2026 12:26:56 PM</t>
+        </is>
+      </c>
+      <c r="K48" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 03:12:22 PM</t>
+        </is>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>1h 3m</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 45m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_03_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_03_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -8004,10 +8004,8 @@
           <t>Himmat  Shrestha</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>9847898946</t>
-        </is>
+      <c r="O41" s="3" t="n">
+        <v>9847898946</v>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
@@ -8083,10 +8081,8 @@
           <t>Router Damage Issue</t>
         </is>
       </c>
-      <c r="AH41" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH41" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI41" s="3" t="inlineStr">
         <is>
@@ -8105,25 +8101,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN41" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
           <t>CDB075</t>
         </is>
       </c>
-      <c r="AP41" s="3" t="inlineStr">
-        <is>
-          <t>85.31133</t>
-        </is>
+      <c r="AP41" s="3" t="n">
+        <v>85.31133</v>
       </c>
       <c r="AQ41" s="3" t="inlineStr"/>
       <c r="AR41" s="3" t="inlineStr">
         <is>
-          <t>Case : Router replacement   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS41" s="3" t="inlineStr">
@@ -8219,10 +8211,8 @@
           <t>Himmat  Shrestha</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>9847898946</t>
-        </is>
+      <c r="O42" s="3" t="n">
+        <v>9847898946</v>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
@@ -8298,10 +8288,8 @@
           <t>Router Damage Issue</t>
         </is>
       </c>
-      <c r="AH42" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH42" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI42" s="3" t="inlineStr">
         <is>
@@ -8320,25 +8308,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN42" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
           <t>CDB075</t>
         </is>
       </c>
-      <c r="AP42" s="3" t="inlineStr">
-        <is>
-          <t>85.31133</t>
-        </is>
+      <c r="AP42" s="3" t="n">
+        <v>85.31133</v>
       </c>
       <c r="AQ42" s="3" t="inlineStr"/>
       <c r="AR42" s="3" t="inlineStr">
         <is>
-          <t>Case : Router replacement   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS42" s="3" t="inlineStr">
@@ -8387,7 +8371,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -10242,7 +10226,7 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Case : Router replacement   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
@@ -10309,7 +10293,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>Case : Router replacement   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H48" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_03_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_03_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW42"/>
+  <dimension ref="A1:AW46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8351,6 +8351,418 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 4:13 PM</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr"/>
+      <c r="J43" s="3" t="inlineStr"/>
+      <c r="K43" s="3" t="inlineStr"/>
+      <c r="L43" s="3" t="inlineStr"/>
+      <c r="M43" s="3" t="inlineStr"/>
+      <c r="N43" s="3" t="inlineStr"/>
+      <c r="O43" s="3" t="inlineStr"/>
+      <c r="P43" s="3" t="inlineStr"/>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr"/>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr"/>
+      <c r="V43" s="3" t="inlineStr"/>
+      <c r="W43" s="3" t="inlineStr"/>
+      <c r="X43" s="3" t="inlineStr"/>
+      <c r="Y43" s="3" t="inlineStr"/>
+      <c r="Z43" s="3" t="inlineStr"/>
+      <c r="AA43" s="3" t="inlineStr"/>
+      <c r="AB43" s="3" t="inlineStr"/>
+      <c r="AC43" s="3" t="inlineStr"/>
+      <c r="AD43" s="3" t="inlineStr"/>
+      <c r="AE43" s="3" t="inlineStr"/>
+      <c r="AF43" s="3" t="inlineStr"/>
+      <c r="AG43" s="3" t="inlineStr"/>
+      <c r="AH43" s="3" t="inlineStr"/>
+      <c r="AI43" s="3" t="inlineStr"/>
+      <c r="AJ43" s="3" t="inlineStr"/>
+      <c r="AK43" s="3" t="inlineStr"/>
+      <c r="AL43" s="3" t="inlineStr"/>
+      <c r="AM43" s="3" t="inlineStr"/>
+      <c r="AN43" s="3" t="inlineStr"/>
+      <c r="AO43" s="3" t="inlineStr"/>
+      <c r="AP43" s="3" t="inlineStr"/>
+      <c r="AQ43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 4:12 PM</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr"/>
+      <c r="J44" s="3" t="inlineStr"/>
+      <c r="K44" s="3" t="inlineStr"/>
+      <c r="L44" s="3" t="inlineStr"/>
+      <c r="M44" s="3" t="inlineStr"/>
+      <c r="N44" s="3" t="inlineStr"/>
+      <c r="O44" s="3" t="inlineStr"/>
+      <c r="P44" s="3" t="inlineStr"/>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr"/>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr"/>
+      <c r="V44" s="3" t="inlineStr"/>
+      <c r="W44" s="3" t="inlineStr"/>
+      <c r="X44" s="3" t="inlineStr"/>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr"/>
+      <c r="AA44" s="3" t="inlineStr"/>
+      <c r="AB44" s="3" t="inlineStr"/>
+      <c r="AC44" s="3" t="inlineStr"/>
+      <c r="AD44" s="3" t="inlineStr"/>
+      <c r="AE44" s="3" t="inlineStr"/>
+      <c r="AF44" s="3" t="inlineStr"/>
+      <c r="AG44" s="3" t="inlineStr"/>
+      <c r="AH44" s="3" t="inlineStr"/>
+      <c r="AI44" s="3" t="inlineStr"/>
+      <c r="AJ44" s="3" t="inlineStr"/>
+      <c r="AK44" s="3" t="inlineStr"/>
+      <c r="AL44" s="3" t="inlineStr"/>
+      <c r="AM44" s="3" t="inlineStr"/>
+      <c r="AN44" s="3" t="inlineStr"/>
+      <c r="AO44" s="3" t="inlineStr"/>
+      <c r="AP44" s="3" t="inlineStr"/>
+      <c r="AQ44" s="3" t="inlineStr"/>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW44" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 4:04 PM</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Case : router  upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr"/>
+      <c r="J45" s="3" t="inlineStr"/>
+      <c r="K45" s="3" t="inlineStr"/>
+      <c r="L45" s="3" t="inlineStr"/>
+      <c r="M45" s="3" t="inlineStr"/>
+      <c r="N45" s="3" t="inlineStr"/>
+      <c r="O45" s="3" t="inlineStr"/>
+      <c r="P45" s="3" t="inlineStr"/>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr"/>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr"/>
+      <c r="V45" s="3" t="inlineStr"/>
+      <c r="W45" s="3" t="inlineStr"/>
+      <c r="X45" s="3" t="inlineStr"/>
+      <c r="Y45" s="3" t="inlineStr"/>
+      <c r="Z45" s="3" t="inlineStr"/>
+      <c r="AA45" s="3" t="inlineStr"/>
+      <c r="AB45" s="3" t="inlineStr"/>
+      <c r="AC45" s="3" t="inlineStr"/>
+      <c r="AD45" s="3" t="inlineStr"/>
+      <c r="AE45" s="3" t="inlineStr"/>
+      <c r="AF45" s="3" t="inlineStr"/>
+      <c r="AG45" s="3" t="inlineStr"/>
+      <c r="AH45" s="3" t="inlineStr"/>
+      <c r="AI45" s="3" t="inlineStr"/>
+      <c r="AJ45" s="3" t="inlineStr"/>
+      <c r="AK45" s="3" t="inlineStr"/>
+      <c r="AL45" s="3" t="inlineStr"/>
+      <c r="AM45" s="3" t="inlineStr"/>
+      <c r="AN45" s="3" t="inlineStr"/>
+      <c r="AO45" s="3" t="inlineStr"/>
+      <c r="AP45" s="3" t="inlineStr"/>
+      <c r="AQ45" s="3" t="inlineStr"/>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
+          <t>Case : router  upgrade   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 4:03 PM</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr"/>
+      <c r="J46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="3" t="inlineStr"/>
+      <c r="M46" s="3" t="inlineStr"/>
+      <c r="N46" s="3" t="inlineStr"/>
+      <c r="O46" s="3" t="inlineStr"/>
+      <c r="P46" s="3" t="inlineStr"/>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr"/>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr"/>
+      <c r="V46" s="3" t="inlineStr"/>
+      <c r="W46" s="3" t="inlineStr"/>
+      <c r="X46" s="3" t="inlineStr"/>
+      <c r="Y46" s="3" t="inlineStr"/>
+      <c r="Z46" s="3" t="inlineStr"/>
+      <c r="AA46" s="3" t="inlineStr"/>
+      <c r="AB46" s="3" t="inlineStr"/>
+      <c r="AC46" s="3" t="inlineStr"/>
+      <c r="AD46" s="3" t="inlineStr"/>
+      <c r="AE46" s="3" t="inlineStr"/>
+      <c r="AF46" s="3" t="inlineStr"/>
+      <c r="AG46" s="3" t="inlineStr"/>
+      <c r="AH46" s="3" t="inlineStr"/>
+      <c r="AI46" s="3" t="inlineStr"/>
+      <c r="AJ46" s="3" t="inlineStr"/>
+      <c r="AK46" s="3" t="inlineStr"/>
+      <c r="AL46" s="3" t="inlineStr"/>
+      <c r="AM46" s="3" t="inlineStr"/>
+      <c r="AN46" s="3" t="inlineStr"/>
+      <c r="AO46" s="3" t="inlineStr"/>
+      <c r="AP46" s="3" t="inlineStr"/>
+      <c r="AQ46" s="3" t="inlineStr"/>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8399,7 +8811,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
@@ -8420,7 +8832,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>51.1%</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_03_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_03_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW46"/>
+  <dimension ref="A1:AW47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8763,6 +8763,109 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 4:27 PM</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr"/>
+      <c r="J47" s="3" t="inlineStr"/>
+      <c r="K47" s="3" t="inlineStr"/>
+      <c r="L47" s="3" t="inlineStr"/>
+      <c r="M47" s="3" t="inlineStr"/>
+      <c r="N47" s="3" t="inlineStr"/>
+      <c r="O47" s="3" t="inlineStr"/>
+      <c r="P47" s="3" t="inlineStr"/>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr"/>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr"/>
+      <c r="V47" s="3" t="inlineStr"/>
+      <c r="W47" s="3" t="inlineStr"/>
+      <c r="X47" s="3" t="inlineStr"/>
+      <c r="Y47" s="3" t="inlineStr"/>
+      <c r="Z47" s="3" t="inlineStr"/>
+      <c r="AA47" s="3" t="inlineStr"/>
+      <c r="AB47" s="3" t="inlineStr"/>
+      <c r="AC47" s="3" t="inlineStr"/>
+      <c r="AD47" s="3" t="inlineStr"/>
+      <c r="AE47" s="3" t="inlineStr"/>
+      <c r="AF47" s="3" t="inlineStr"/>
+      <c r="AG47" s="3" t="inlineStr"/>
+      <c r="AH47" s="3" t="inlineStr"/>
+      <c r="AI47" s="3" t="inlineStr"/>
+      <c r="AJ47" s="3" t="inlineStr"/>
+      <c r="AK47" s="3" t="inlineStr"/>
+      <c r="AL47" s="3" t="inlineStr"/>
+      <c r="AM47" s="3" t="inlineStr"/>
+      <c r="AN47" s="3" t="inlineStr"/>
+      <c r="AO47" s="3" t="inlineStr"/>
+      <c r="AP47" s="3" t="inlineStr"/>
+      <c r="AQ47" s="3" t="inlineStr"/>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8811,7 +8914,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3">
@@ -8832,7 +8935,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_03_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_03_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW47"/>
+  <dimension ref="A1:AW48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -8866,6 +8866,109 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 4:41 PM</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr"/>
+      <c r="K48" s="3" t="inlineStr"/>
+      <c r="L48" s="3" t="inlineStr"/>
+      <c r="M48" s="3" t="inlineStr"/>
+      <c r="N48" s="3" t="inlineStr"/>
+      <c r="O48" s="3" t="inlineStr"/>
+      <c r="P48" s="3" t="inlineStr"/>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr"/>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr"/>
+      <c r="V48" s="3" t="inlineStr"/>
+      <c r="W48" s="3" t="inlineStr"/>
+      <c r="X48" s="3" t="inlineStr"/>
+      <c r="Y48" s="3" t="inlineStr"/>
+      <c r="Z48" s="3" t="inlineStr"/>
+      <c r="AA48" s="3" t="inlineStr"/>
+      <c r="AB48" s="3" t="inlineStr"/>
+      <c r="AC48" s="3" t="inlineStr"/>
+      <c r="AD48" s="3" t="inlineStr"/>
+      <c r="AE48" s="3" t="inlineStr"/>
+      <c r="AF48" s="3" t="inlineStr"/>
+      <c r="AG48" s="3" t="inlineStr"/>
+      <c r="AH48" s="3" t="inlineStr"/>
+      <c r="AI48" s="3" t="inlineStr"/>
+      <c r="AJ48" s="3" t="inlineStr"/>
+      <c r="AK48" s="3" t="inlineStr"/>
+      <c r="AL48" s="3" t="inlineStr"/>
+      <c r="AM48" s="3" t="inlineStr"/>
+      <c r="AN48" s="3" t="inlineStr"/>
+      <c r="AO48" s="3" t="inlineStr"/>
+      <c r="AP48" s="3" t="inlineStr"/>
+      <c r="AQ48" s="3" t="inlineStr"/>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8914,7 +9017,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3">
@@ -8935,7 +9038,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>48.9%</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_03_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_03_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW48"/>
+  <dimension ref="A1:AW49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -8969,6 +8969,217 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 4:56 PM</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>TKT1356367</t>
+        </is>
+      </c>
+      <c r="K49" s="3" t="inlineStr">
+        <is>
+          <t>Aashish Gurung</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>Aashish Gurung</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>9810040058</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:44:54 AM</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>9881395762</t>
+        </is>
+      </c>
+      <c r="V49" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:44:54 AM</t>
+        </is>
+      </c>
+      <c r="W49" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 04:56:25 PM</t>
+        </is>
+      </c>
+      <c r="X49" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y49" s="3" t="inlineStr">
+        <is>
+          <t>27.69028</t>
+        </is>
+      </c>
+      <c r="Z49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA49" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB49" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC49" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD49" s="3" t="inlineStr"/>
+      <c r="AE49" s="3" t="inlineStr">
+        <is>
+          <t>Kuleshwore Gaurisankhar sadak, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF49" s="3" t="inlineStr">
+        <is>
+          <t>aashishgurung878@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG49" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH49" s="3" t="inlineStr"/>
+      <c r="AI49" s="3" t="inlineStr">
+        <is>
+          <t>05:12 hour</t>
+        </is>
+      </c>
+      <c r="AJ49" s="3" t="inlineStr"/>
+      <c r="AK49" s="3" t="inlineStr"/>
+      <c r="AL49" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM49" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN49" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO49" s="3" t="inlineStr">
+        <is>
+          <t>CDB174</t>
+        </is>
+      </c>
+      <c r="AP49" s="3" t="inlineStr">
+        <is>
+          <t>85.29317</t>
+        </is>
+      </c>
+      <c r="AQ49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>5h 11m</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>5h 11m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8980,7 +9191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -8989,7 +9200,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -9017,7 +9228,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
@@ -9027,7 +9238,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -9038,7 +9249,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -9050,7 +9261,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2h 8m</t>
+          <t>2h 16m</t>
         </is>
       </c>
     </row>
@@ -9062,7 +9273,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>20h 44m</t>
+          <t>20h 5m</t>
         </is>
       </c>
     </row>
@@ -9103,14 +9314,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -9234,14 +9445,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>72.4%</t>
         </is>
       </c>
     </row>
@@ -10945,6 +11156,73 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>TKT1356367</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Aashish Gurung</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:44:54 AM</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 11:44:54 AM</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 04:56:25 PM</t>
+        </is>
+      </c>
+      <c r="L49" s="5" t="inlineStr">
+        <is>
+          <t>5h 11m</t>
+        </is>
+      </c>
+      <c r="M49" s="5" t="inlineStr">
+        <is>
+          <t>5h 11m</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/audit_report_ALL_TEAM_03_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_03_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW49"/>
+  <dimension ref="A1:AW51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -9036,10 +9036,8 @@
           <t>Aashish Gurung</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr">
-        <is>
-          <t>9810040058</t>
-        </is>
+      <c r="O49" s="3" t="n">
+        <v>9810040058</v>
       </c>
       <c r="P49" s="3" t="inlineStr">
         <is>
@@ -9133,48 +9131,250 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN49" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN49" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO49" s="3" t="inlineStr">
         <is>
           <t>CDB174</t>
         </is>
       </c>
-      <c r="AP49" s="3" t="inlineStr">
-        <is>
-          <t>85.29317</t>
-        </is>
+      <c r="AP49" s="3" t="n">
+        <v>85.29317</v>
       </c>
       <c r="AQ49" s="3" t="inlineStr"/>
       <c r="AR49" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>5h 11m</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>5h 11m</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS49" s="3" t="inlineStr">
-        <is>
-          <t>5h 11m</t>
-        </is>
-      </c>
-      <c r="AT49" s="3" t="inlineStr">
-        <is>
-          <t>5h 11m</t>
-        </is>
-      </c>
-      <c r="AU49" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV49" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 5:14 PM</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr"/>
+      <c r="J50" s="3" t="inlineStr"/>
+      <c r="K50" s="3" t="inlineStr"/>
+      <c r="L50" s="3" t="inlineStr"/>
+      <c r="M50" s="3" t="inlineStr"/>
+      <c r="N50" s="3" t="inlineStr"/>
+      <c r="O50" s="3" t="inlineStr"/>
+      <c r="P50" s="3" t="inlineStr"/>
+      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr"/>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr"/>
+      <c r="V50" s="3" t="inlineStr"/>
+      <c r="W50" s="3" t="inlineStr"/>
+      <c r="X50" s="3" t="inlineStr"/>
+      <c r="Y50" s="3" t="inlineStr"/>
+      <c r="Z50" s="3" t="inlineStr"/>
+      <c r="AA50" s="3" t="inlineStr"/>
+      <c r="AB50" s="3" t="inlineStr"/>
+      <c r="AC50" s="3" t="inlineStr"/>
+      <c r="AD50" s="3" t="inlineStr"/>
+      <c r="AE50" s="3" t="inlineStr"/>
+      <c r="AF50" s="3" t="inlineStr"/>
+      <c r="AG50" s="3" t="inlineStr"/>
+      <c r="AH50" s="3" t="inlineStr"/>
+      <c r="AI50" s="3" t="inlineStr"/>
+      <c r="AJ50" s="3" t="inlineStr"/>
+      <c r="AK50" s="3" t="inlineStr"/>
+      <c r="AL50" s="3" t="inlineStr"/>
+      <c r="AM50" s="3" t="inlineStr"/>
+      <c r="AN50" s="3" t="inlineStr"/>
+      <c r="AO50" s="3" t="inlineStr"/>
+      <c r="AP50" s="3" t="inlineStr"/>
+      <c r="AQ50" s="3" t="inlineStr"/>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>03 Oct 2026 5:13 PM</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr"/>
+      <c r="J51" s="3" t="inlineStr"/>
+      <c r="K51" s="3" t="inlineStr"/>
+      <c r="L51" s="3" t="inlineStr"/>
+      <c r="M51" s="3" t="inlineStr"/>
+      <c r="N51" s="3" t="inlineStr"/>
+      <c r="O51" s="3" t="inlineStr"/>
+      <c r="P51" s="3" t="inlineStr"/>
+      <c r="Q51" s="3" t="inlineStr"/>
+      <c r="R51" s="3" t="inlineStr"/>
+      <c r="S51" s="3" t="inlineStr"/>
+      <c r="T51" s="3" t="inlineStr"/>
+      <c r="U51" s="3" t="inlineStr"/>
+      <c r="V51" s="3" t="inlineStr"/>
+      <c r="W51" s="3" t="inlineStr"/>
+      <c r="X51" s="3" t="inlineStr"/>
+      <c r="Y51" s="3" t="inlineStr"/>
+      <c r="Z51" s="3" t="inlineStr"/>
+      <c r="AA51" s="3" t="inlineStr"/>
+      <c r="AB51" s="3" t="inlineStr"/>
+      <c r="AC51" s="3" t="inlineStr"/>
+      <c r="AD51" s="3" t="inlineStr"/>
+      <c r="AE51" s="3" t="inlineStr"/>
+      <c r="AF51" s="3" t="inlineStr"/>
+      <c r="AG51" s="3" t="inlineStr"/>
+      <c r="AH51" s="3" t="inlineStr"/>
+      <c r="AI51" s="3" t="inlineStr"/>
+      <c r="AJ51" s="3" t="inlineStr"/>
+      <c r="AK51" s="3" t="inlineStr"/>
+      <c r="AL51" s="3" t="inlineStr"/>
+      <c r="AM51" s="3" t="inlineStr"/>
+      <c r="AN51" s="3" t="inlineStr"/>
+      <c r="AO51" s="3" t="inlineStr"/>
+      <c r="AP51" s="3" t="inlineStr"/>
+      <c r="AQ51" s="3" t="inlineStr"/>
+      <c r="AR51" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW51" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -9200,7 +9400,7 @@
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -9228,7 +9428,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -9249,7 +9449,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>48.0%</t>
         </is>
       </c>
     </row>
@@ -11189,7 +11389,7 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
